--- a/StructureDefinition-Halso--och-sjukvardspersonal-Halso--och-sjukvardsperson.xlsx
+++ b/StructureDefinition-Halso--och-sjukvardspersonal-Halso--och-sjukvardsperson.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Halso--och-sjukvardspersonal-Halso--och-sjukvardsperson.xlsx
+++ b/StructureDefinition-Halso--och-sjukvardspersonal-Halso--och-sjukvardsperson.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="103">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Hälso- och sjukvårdspersonal : Hälso- och sjukvårdspersonal).</t>
+    <t>Klassen hälso- och sjukvårdspersonal håller information om person som i sitt yrke utför hälso- och sjukvård.
+Hälso- och sjukvårdspersonal är oftast anställd av en vårdgivare. En vårdgivare kan ha anställd hälso- och sjukvårdspersonal, och ibland, som till exempel för enskild näringsidkare, kan rollerna sammanfalla.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -263,6 +264,9 @@
     <t>Source attribute: id; renamed from reserved FSH name 'id'</t>
   </si>
   <si>
+    <t>Angivelse av identitetsbeteckning för hälso- och sjukvårdspersonal.</t>
+  </si>
+  <si>
     <t>Halso--och-sjukvardspersonal-Halso--och-sjukvardsperson.namn</t>
   </si>
   <si>
@@ -273,6 +277,10 @@
     <t>Source attribute: namn</t>
   </si>
   <si>
+    <t>Angivelse av personnamn sammanslaget enligt formatet "Mellannamn Efternamn, Förnamn".
+Om flera namn av samma typ förekommer ska dessa separeras med mellanslag.</t>
+  </si>
+  <si>
     <t>Halso--och-sjukvardspersonal-Halso--och-sjukvardsperson.befattning</t>
   </si>
   <si>
@@ -281,6 +289,11 @@
   </si>
   <si>
     <t>Source attribute: befattning</t>
+  </si>
+  <si>
+    <t>Kod för hälso- och sjukvårdspersonalens befattning.
+Om möjligt ska KV Befattning användas (notera dock att befattning INTE alltid kan jämställas med roll i detta avseende).
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
   </si>
   <si>
     <t>Halso--och-sjukvardspersonal-Halso--och-sjukvardsperson.harMedicinsktAnsvarig</t>
@@ -906,7 +919,7 @@
         <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -974,10 +987,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1000,13 +1013,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1057,7 +1070,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
@@ -1074,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1100,13 +1113,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1157,7 +1170,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1174,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1200,13 +1213,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1257,7 +1270,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1274,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1300,13 +1313,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1357,7 +1370,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1374,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1400,13 +1413,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1457,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1474,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1500,13 +1513,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1557,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
